--- a/schedule.xlsx
+++ b/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbgurbisz/Documents/SMR-monitoring/MRNE395-2025FA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF97DFE5-7112-4249-BD96-B47746FC418C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EABD89C-67D6-A240-85A2-3A51808286F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31340" yWindow="1560" windowWidth="28800" windowHeight="17500" xr2:uid="{4525DE01-5AFE-3449-9459-0416C5161635}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{4525DE01-5AFE-3449-9459-0416C5161635}"/>
   </bookViews>
   <sheets>
     <sheet name="schedule" sheetId="1" r:id="rId1"/>
@@ -33,14 +33,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>DIY monitoring technology</t>
-  </si>
-  <si>
     <t>week</t>
   </si>
   <si>
@@ -119,9 +116,6 @@
     <t>[Water quality criteria and SAV](https://smr-monitoring.github.io/lesson-plans/02-wq-criteria.html)</t>
   </si>
   <si>
-    <t>[Discrete monitoring](https://smr-monitoring.github.io/lesson-plans/10-discrete-boat.html)</t>
-  </si>
-  <si>
     <t>HW 1</t>
   </si>
   <si>
@@ -186,6 +180,18 @@
   </si>
   <si>
     <t>CONMON at SMCM cont.</t>
+  </si>
+  <si>
+    <t>CBG out - no class</t>
+  </si>
+  <si>
+    <t>Exam review</t>
+  </si>
+  <si>
+    <t>meet in River Center classroom; be prepared to go outside</t>
+  </si>
+  <si>
+    <t>meet in SH 112</t>
   </si>
 </sst>
 </file>
@@ -1066,19 +1072,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -1086,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1100,13 +1106,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1114,16 +1120,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1131,13 +1137,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1145,16 +1151,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1162,16 +1168,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
         <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1179,16 +1185,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1196,16 +1202,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1213,16 +1219,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1230,16 +1236,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1247,16 +1253,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1264,10 +1270,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1275,10 +1284,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1286,13 +1295,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1300,21 +1309,27 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
